--- a/summer_camps/004_summer_camp_admission_checklist_form_template--summer_camps.xlsx
+++ b/summer_camps/004_summer_camp_admission_checklist_form_template--summer_camps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_first_name</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_first</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_2</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Phone</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_3</t>
+          <t>emergency_contact_name</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>emergency_contact_name</t>
+          <t>Emergency Contact Name</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,63 +676,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_4</t>
+          <t>emergency_contact_relationship</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>Emergency Contact Relationship</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_5</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>emergency_contact_phone</t>
+          <t>Medical Condition/Allergy</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_6</t>
+          <t>medical_condition_details</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>allergy_or_medical_condition</t>
+          <t>Medical Condition Details</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_7</t>
+          <t>medical_supervision</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>medical_condition_details</t>
+          <t>Medical Supervision Required</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_8</t>
+          <t>insurance_provider</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>medical_supervision</t>
+          <t>Insurance Provider</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_9</t>
+          <t>insurance_plan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>camper_medical_insurance</t>
+          <t>Insurance Plan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_10</t>
+          <t>medical_insurance_provider_name</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>medical_insurance_provider</t>
+          <t>Medical Insurance Provider Name</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_11</t>
+          <t>medical_insurance_provider_id</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>camper_medical_insurance_provider</t>
+          <t>Medical Insurance Provider ID</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_12</t>
+          <t>relationship_type</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>camper_medical_insurance_provider_id</t>
+          <t>Relationship Type</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_13</t>
+          <t>relationship_type_other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>parent_permission</t>
+          <t>Relationship Type Other</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_14</t>
+          <t>insurance_plan_id</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship</t>
+          <t>Insurance Plan ID</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>summer_camp_admission_checklist_form_template_last_15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>summer_camp_admission_checklist_form_template_last_16</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>emergency_contact_relationship_other_relation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>summer_camp_admission_checklist_form_template_last_17</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>camper_medical_insurance_plan</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>summer_camp_admission_checklist_form_template_last_18</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>camper_medical_insurance_plan_id</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>summer_camp_admission_checklist_form_template_last_19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>camper_medical_insurance_provider</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>summer_camp_admission_checklist_form_template_last_20</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>camper_medical_insurance_provider_id</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>summer_camp_admission_checklist_form_template_last_21</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>camper_medical_insurance_other</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,134 +965,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_9_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_9_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>guardian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Guardian</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_13_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_13_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>guardian</t>
+          <t>food_allergy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Guardian</t>
+          <t>Food Allergy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_13_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>guardian_1</t>
+          <t>environmental_allergy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Guardian 1</t>
+          <t>Environmental Allergy</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_13_choices</t>
+          <t>medical_supervision_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>guardian_2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Guardian 2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_14_choices</t>
+          <t>medical_supervision_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>parent</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Parent</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>summer_camp_admission_checklist_form_template_last_14_choices</t>
+          <t>relationship_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>parent</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Parent</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>relationship_type_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>guardian</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Guardian</t>
         </is>
